--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0222.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0222.xlsx
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bí ẩn với khả năng hấp thụ mọi âm thanh. Hiện đang trên hành trình tìm lại ký ức đã mất.</t>
+          <t>Một Resonator bí ẩn với khả năng hấp thụ mọi âm thanh. Hiện đang trên hành trình tìm lại ký ức đã mất.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bí ẩn với khả năng hấp thụ mọi âm thanh. Hiện đang trên hành trình tìm lại ký ức đã mất.</t>
+          <t>Một Resonator bí ẩn với khả năng hấp thụ mọi âm thanh. Hiện đang trên hành trình tìm lại ký ức đã mất.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Trừ khi có Cộng Hưởng Giả can thiệp vào?</t>
+          <t>Trừ khi có Resonator can thiệp vào?</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Ai lại muốn ta chết chứ?</t>
+          <t>Ai lại muốn tao chết chứ?</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 14.000 điểm trong If Bạn Gaze Into the Abyss of Dreams.</t>
+          <t>Tổng cộng đạt 14.000 điểm trong If You Gaze Into the Abyss of Dreams.</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Sử dụng Rover: Aero để vượt qua Tháp Cộng Hưởng &amp; Tháp Vọng Âm Tầng 4 trong "Tháp Nghịch Cảnh: Vùng Nguy Hiểm".</t>
+          <t>Sử dụng Vận Mệnh Giả: Aero để vượt qua Tháp Cộng Hưởng &amp; Tháp Vọng Âm Tầng 4 trong "Tháp Nghịch Cảnh: Vùng Nguy Hiểm".</t>
         </is>
       </c>
     </row>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Zani là đồng đội không thể thiếu của ta. Còn mấy người kia? Chỉ là dân dự bị thôi.</t>
+          <t>Zani là đồng đội không thể thiếu của tao. Còn mấy người kia? Chỉ là dân dự bị thôi.</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Đồng hành mới!</t>
+          <t>Đồng Hành Mới!</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>&lt;color=#00faaeff&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -20803,7 +20803,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Triệu tập Cộng Hưởng Giả 10 lần</t>
+          <t>Triệu tập Resonator 10 lần</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Triệu tập Cộng Hưởng Giả 20 lần</t>
+          <t>Triệu tập Resonator 20 lần</t>
         </is>
       </c>
     </row>
@@ -21715,7 +21715,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Tổng cộng triệu tập Cộng Hưởng Giả 60 lần</t>
+          <t>Tổng cộng triệu tập Resonator 60 lần</t>
         </is>
       </c>
     </row>
@@ -21780,7 +21780,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Tổng cộng triệu tập Cộng Hưởng Giả 90 lần</t>
+          <t>Tổng cộng triệu tập Resonator 90 lần</t>
         </is>
       </c>
     </row>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Triệu tập Cộng Hưởng Giả 40 lần (có thể lặp lại)</t>
+          <t>Triệu tập Resonator 40 lần (có thể lặp lại)</t>
         </is>
       </c>
     </row>
@@ -22495,7 +22495,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Flash&lt;/color&gt; - Khi Giai Đoạn Chiến Đấu bắt đầu, dịch chuyển Tổ Tacet này đến Khu Hậu Cảnh của đối phương.</t>
+          <t>&lt;color=#e4c69b&gt;Thần Tốc&lt;/color&gt; - Khi Giai Đoạn Chiến Đấu bắt đầu, dịch chuyển Tổ Tacet này đến Khu Hậu Cảnh của đối phương.</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22560,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Recharge&lt;/color&gt; - Mỗi lần sử dụng Biến Hóa, bạn nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng.</t>
+          <t>&lt;color=#e4c69b&gt;Nạp Năng&lt;/color&gt; - Mỗi lần sử dụng Biến Hóa, bạn nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Conversion&lt;/color&gt; - Mỗi khi sử dụng Biến Đổi, bạn rút một lá bài và sau đó đặt một lá bài trên tay trở lại bộ bài.</t>
+          <t>&lt;color=#e4c69b&gt;Conversion&lt;/color&gt; - Mỗi khi sử dụng Transform, bạn rút một lá bài và sau đó đặt một lá bài trên tay trở lại bộ bài.</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Versatility&lt;/color&gt; - Khi Đa Dạng được kích hoạt, Cộng Hưởng Giả này có thể được Điều Chỉnh bởi bất kỳ Cộng Hưởng Giả Thường nào mà không bị hạn chế.</t>
+          <t>&lt;color=#e4c69b&gt;Đa Dạng&lt;/color&gt; - Khi Đa Dạng được kích hoạt, Cộng Hưởng Giả này có thể được Điều Chỉnh bởi bất kỳ Cộng Hưởng Giả Thường nào mà không bị hạn chế.</t>
         </is>
       </c>
     </row>
@@ -23795,7 +23795,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Fight!</t>
+          <t>Chiến đấu!</t>
         </is>
       </c>
     </row>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Round {0}</t>
+          <t>Vòng {0}</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>&lt;color=#ff0000&gt;Lv. {0}&lt;/color&gt;/Cấp {1}</t>
+          <t>&lt;color=#ff0000&gt;Cấp {0}&lt;/color&gt;/Cấp {1}</t>
         </is>
       </c>
     </row>
@@ -25225,7 +25225,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>&lt;color=#ff0000&gt;Lv. {0}&lt;/color&gt;/Cấp {1}</t>
+          <t>&lt;color=#ff0000&gt;Cấp {0}&lt;/color&gt;/Cấp {1}</t>
         </is>
       </c>
     </row>
@@ -25290,7 +25290,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>&lt;color=#ff0000&gt;{0}s&lt;/color&gt;/{1} giây</t>
+          <t>&lt;color=#ff0000&gt;{0} giây&lt;/color&gt;/{1} giây</t>
         </is>
       </c>
     </row>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>&lt;color=#e2524c&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chi phí 4 Tiếng Vang bị khóa. Hoàn thành nhiệm vụ để mở khóa.</t>
+          <t>Chi phí 4 Echo bị khóa. Hoàn thành nhiệm vụ để mở khóa.</t>
         </is>
       </c>
     </row>
